--- a/pie_chart.xlsx
+++ b/pie_chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5D4553-CE7D-41DC-A404-9B8351C6562E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8747B2A-6779-49F6-AD35-FFC8ECCB7CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="13">
   <si>
     <t>Transit</t>
   </si>
@@ -54,6 +54,34 @@
   </si>
   <si>
     <t xml:space="preserve">ROV Maintenance </t>
+  </si>
+  <si>
+    <t>Task</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A09</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A06</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -107,7 +135,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +148,9 @@
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -402,448 +433,506 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.8984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.8984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.59765625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="13.8984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.8984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.296875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>45890</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3">
         <v>0.3430555555555555</v>
       </c>
-      <c r="C2" s="3">
-        <v>0</v>
-      </c>
       <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
         <v>0.1388888888888889</v>
       </c>
-      <c r="E2" s="3">
-        <v>0</v>
-      </c>
       <c r="F2" s="3">
-        <v>2.0833333333333259E-2</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>2.0833333333333259E-2</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>45892</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4">
         <v>0.33263888888888893</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
       <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
         <v>0.14861111111111108</v>
       </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
       <c r="F3" s="4">
-        <v>2.0833333333333259E-2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>2.0833333333333259E-2</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>45893</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4">
         <v>0.47847222222222224</v>
       </c>
-      <c r="C4" s="4">
+      <c r="D4" s="4">
         <v>4.3055555555555514E-2</v>
       </c>
-      <c r="D4" s="4">
+      <c r="E4" s="4">
         <v>6.1805555555555558E-2</v>
       </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
       <c r="F4" s="4">
-        <v>2.0833333333333259E-2</v>
+        <v>0</v>
       </c>
       <c r="G4" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>2.0833333333333259E-2</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>45894</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="4">
         <v>0.22430555555555556</v>
       </c>
-      <c r="C5" s="4">
+      <c r="D5" s="4">
         <v>8.6805555555555525E-2</v>
       </c>
-      <c r="D5" s="4">
+      <c r="E5" s="4">
         <v>0.10972222222222222</v>
       </c>
-      <c r="E5" s="4">
+      <c r="F5" s="4">
         <v>8.1249999999999989E-2</v>
       </c>
-      <c r="F5" s="4">
-        <v>2.0833333333333259E-2</v>
-      </c>
       <c r="G5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>2.0833333333333259E-2</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>45895</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4">
         <v>0.31736111111111109</v>
       </c>
-      <c r="C6" s="4">
+      <c r="D6" s="4">
         <v>2.9166666666666674E-2</v>
       </c>
-      <c r="D6" s="4">
+      <c r="E6" s="4">
         <v>7.5694444444444398E-2</v>
       </c>
-      <c r="E6" s="4">
+      <c r="F6" s="4">
         <v>1.041666666666663E-2</v>
       </c>
-      <c r="F6" s="4">
-        <v>2.0833333333333259E-2</v>
-      </c>
       <c r="G6" s="4">
+        <v>2.0833333333333259E-2</v>
+      </c>
+      <c r="H6" s="4">
         <v>2.083333333333337E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>45897</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4">
         <v>0.26319444444444451</v>
       </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
       <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
         <v>0.13263888888888892</v>
       </c>
-      <c r="E7" s="4">
+      <c r="F7" s="4">
         <v>1.8749999999999933E-2</v>
       </c>
-      <c r="F7" s="4">
-        <v>2.0833333333333259E-2</v>
-      </c>
       <c r="G7" s="4">
+        <v>2.0833333333333259E-2</v>
+      </c>
+      <c r="H7" s="4">
         <v>2.083333333333337E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>45898</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="4">
         <v>0.34930555555555554</v>
       </c>
-      <c r="C8" s="4">
+      <c r="D8" s="4">
         <v>1.5277777777777835E-2</v>
       </c>
-      <c r="D8" s="4">
+      <c r="E8" s="4">
         <v>8.3333333333333315E-2</v>
       </c>
-      <c r="E8" s="4">
+      <c r="F8" s="4">
         <v>1.2499999999999956E-2</v>
       </c>
-      <c r="F8" s="4">
-        <v>2.0833333333333259E-2</v>
-      </c>
       <c r="G8" s="4">
+        <v>2.0833333333333259E-2</v>
+      </c>
+      <c r="H8" s="4">
         <v>9.7222222222221877E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>45901</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="4">
         <v>0.27569444444444441</v>
       </c>
-      <c r="C9" s="4">
+      <c r="D9" s="4">
         <v>1.7361111111111105E-2</v>
       </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
       <c r="E9" s="4">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
         <v>0.12638888888888888</v>
       </c>
-      <c r="F9" s="4">
-        <v>2.0833333333333259E-2</v>
-      </c>
       <c r="G9" s="4">
+        <v>2.0833333333333259E-2</v>
+      </c>
+      <c r="H9" s="4">
         <v>1.8749999999999989E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>45902</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="4">
         <v>0.3118055555555555</v>
       </c>
-      <c r="C10" s="4">
-        <v>0</v>
-      </c>
       <c r="D10" s="4">
         <v>0</v>
       </c>
       <c r="E10" s="4">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4">
         <v>6.1111111111111116E-2</v>
       </c>
-      <c r="F10" s="4">
-        <v>2.0833333333333259E-2</v>
-      </c>
       <c r="G10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>2.0833333333333259E-2</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>45903</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="4">
         <v>0.25833333333333341</v>
       </c>
-      <c r="C11" s="4">
-        <v>0</v>
-      </c>
       <c r="D11" s="4">
         <v>0</v>
       </c>
       <c r="E11" s="4">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4">
         <v>0.16041666666666671</v>
       </c>
-      <c r="F11" s="4">
+      <c r="G11" s="4">
         <v>2.5000000000000022E-2</v>
       </c>
-      <c r="G11" s="4">
+      <c r="H11" s="4">
         <v>7.7083333333333337E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>45904</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="4">
         <v>0.42291666666666661</v>
       </c>
-      <c r="C12" s="4">
-        <v>0</v>
-      </c>
       <c r="D12" s="4">
         <v>0</v>
       </c>
       <c r="E12" s="4">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4">
         <v>9.5833333333333381E-2</v>
       </c>
-      <c r="F12" s="4">
+      <c r="G12" s="4">
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>45906</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4">
         <v>0.40486111111111106</v>
       </c>
-      <c r="C13" s="4">
-        <v>0</v>
-      </c>
       <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
         <v>3.0555555555555558E-2</v>
       </c>
-      <c r="E13" s="4">
+      <c r="F13" s="4">
         <v>7.9861111111111105E-2</v>
       </c>
-      <c r="F13" s="4">
-        <v>2.0833333333333259E-2</v>
-      </c>
       <c r="G13" s="4">
+        <v>2.0833333333333259E-2</v>
+      </c>
+      <c r="H13" s="4">
         <v>2.083333333333337E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>45907</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4">
         <v>0.27291666666666664</v>
       </c>
-      <c r="C14" s="4">
-        <v>0</v>
-      </c>
       <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
         <v>4.8611111111111105E-2</v>
       </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
       <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
         <v>2.083333333333337E-2</v>
       </c>
-      <c r="G14" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>45908</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="4">
         <v>0.32569444444444445</v>
       </c>
-      <c r="C15" s="4">
-        <v>2.0833333333333259E-2</v>
-      </c>
       <c r="D15" s="4">
+        <v>2.0833333333333259E-2</v>
+      </c>
+      <c r="E15" s="4">
         <v>0.11458333333333331</v>
       </c>
-      <c r="E15" s="4">
+      <c r="F15" s="4">
         <v>6.9444444444445308E-3</v>
       </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
       <c r="G15" s="4">
-        <v>2.0833333333333259E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>2.0833333333333259E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>45909</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="4">
         <v>0.31805555555555565</v>
       </c>
-      <c r="C16" s="4">
+      <c r="D16" s="4">
         <v>1.3888888888888895E-2</v>
       </c>
-      <c r="D16" s="4">
+      <c r="E16" s="4">
         <v>5.7638888888888906E-2</v>
       </c>
-      <c r="E16" s="4">
+      <c r="F16" s="4">
         <v>6.9444444444444198E-3</v>
       </c>
-      <c r="F16" s="4">
+      <c r="G16" s="4">
         <v>2.083333333333337E-2</v>
       </c>
-      <c r="G16" s="4">
+      <c r="H16" s="4">
         <v>1.7361111111111105E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>45910</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="4">
         <v>0.27916666666666667</v>
       </c>
-      <c r="C17" s="4">
-        <v>0</v>
-      </c>
       <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4">
         <v>0.16319444444444448</v>
       </c>
-      <c r="E17" s="4">
+      <c r="F17" s="4">
         <v>3.4722222222222099E-3</v>
       </c>
-      <c r="F17" s="4">
+      <c r="G17" s="4">
         <v>2.083333333333337E-2</v>
       </c>
-      <c r="G17" s="4">
+      <c r="H17" s="4">
         <v>9.7222222222221877E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>45911</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="4">
         <v>0.34097222222222223</v>
       </c>
-      <c r="C18" s="4">
+      <c r="D18" s="4">
         <v>3.9583333333333359E-2</v>
       </c>
-      <c r="D18" s="4">
+      <c r="E18" s="4">
         <v>3.819444444444442E-2</v>
       </c>
-      <c r="E18" s="4">
+      <c r="F18" s="4">
         <v>1.6666666666666663E-2</v>
       </c>
-      <c r="F18" s="4">
+      <c r="G18" s="4">
         <v>2.083333333333337E-2</v>
       </c>
-      <c r="G18" s="4">
+      <c r="H18" s="4">
         <v>6.9444444444444753E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>45912</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="4">
         <v>0.29374999999999996</v>
       </c>
-      <c r="C19" s="4">
+      <c r="D19" s="4">
         <v>6.9444444444444753E-3</v>
       </c>
-      <c r="D19" s="4">
+      <c r="E19" s="4">
         <v>0.14166666666666666</v>
       </c>
-      <c r="E19" s="4">
+      <c r="F19" s="4">
         <v>1.3888888888888951E-2</v>
       </c>
-      <c r="F19" s="4">
-        <v>2.0833333333333259E-2</v>
-      </c>
       <c r="G19" s="4">
+        <v>2.0833333333333259E-2</v>
+      </c>
+      <c r="H19" s="4">
         <v>9.0277777777778012E-3</v>
       </c>
     </row>
